--- a/data_raw/CME_ETHUSD_RR_latest.xlsx
+++ b/data_raw/CME_ETHUSD_RR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D793"/>
+  <dimension ref="A1:D797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13122,6 +13122,70 @@
         <v>2499.11</v>
       </c>
     </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B794" t="n">
+        <v>2502.32</v>
+      </c>
+      <c r="C794" t="n">
+        <v>2511.96</v>
+      </c>
+      <c r="D794" t="n">
+        <v>2491.42</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B795" t="n">
+        <v>2502.38</v>
+      </c>
+      <c r="C795" t="n">
+        <v>2533.47</v>
+      </c>
+      <c r="D795" t="n">
+        <v>2500.32</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B796" t="n">
+        <v>2526.87</v>
+      </c>
+      <c r="C796" t="n">
+        <v>2513.73</v>
+      </c>
+      <c r="D796" t="n">
+        <v>2566.68</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B797" t="n">
+        <v>2516.84</v>
+      </c>
+      <c r="C797" t="n">
+        <v>2506.26</v>
+      </c>
+      <c r="D797" t="n">
+        <v>2528.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/CME_ETHUSD_RR_latest.xlsx
+++ b/data_raw/CME_ETHUSD_RR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D797"/>
+  <dimension ref="A1:D800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13186,6 +13186,54 @@
         <v>2528.82</v>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B798" t="n">
+        <v>2429.05</v>
+      </c>
+      <c r="C798" t="n">
+        <v>2427.43</v>
+      </c>
+      <c r="D798" t="n">
+        <v>2504.46</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B799" t="n">
+        <v>2372.29</v>
+      </c>
+      <c r="C799" t="n">
+        <v>2452.47</v>
+      </c>
+      <c r="D799" t="n">
+        <v>2365.98</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B800" t="n">
+        <v>2466.78</v>
+      </c>
+      <c r="C800" t="n">
+        <v>2406.39</v>
+      </c>
+      <c r="D800" t="n">
+        <v>2451.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/CME_ETHUSD_RR_latest.xlsx
+++ b/data_raw/CME_ETHUSD_RR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D800"/>
+  <dimension ref="A1:D804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13234,6 +13234,70 @@
         <v>2451.24</v>
       </c>
     </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B801" t="n">
+        <v>2422.74</v>
+      </c>
+      <c r="C801" t="n">
+        <v>2414.27</v>
+      </c>
+      <c r="D801" t="n">
+        <v>2431.05</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B802" t="n">
+        <v>2379.77</v>
+      </c>
+      <c r="C802" t="n">
+        <v>2350.28</v>
+      </c>
+      <c r="D802" t="n">
+        <v>2407.13</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B803" t="n">
+        <v>2395.78</v>
+      </c>
+      <c r="C803" t="n">
+        <v>2395.93</v>
+      </c>
+      <c r="D803" t="n">
+        <v>2431.51</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B804" t="n">
+        <v>2453.74</v>
+      </c>
+      <c r="C804" t="n">
+        <v>2432.57</v>
+      </c>
+      <c r="D804" t="n">
+        <v>2390.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/CME_ETHUSD_RR_latest.xlsx
+++ b/data_raw/CME_ETHUSD_RR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D804"/>
+  <dimension ref="A1:D807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13298,6 +13298,54 @@
         <v>2390.6</v>
       </c>
     </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B805" t="n">
+        <v>2476.68</v>
+      </c>
+      <c r="C805" t="n">
+        <v>2492.77</v>
+      </c>
+      <c r="D805" t="n">
+        <v>2446.14</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B806" t="n">
+        <v>2405.55</v>
+      </c>
+      <c r="C806" t="n">
+        <v>2382.46</v>
+      </c>
+      <c r="D806" t="n">
+        <v>2427.21</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B807" t="n">
+        <v>2400.35</v>
+      </c>
+      <c r="C807" t="n">
+        <v>2394.35</v>
+      </c>
+      <c r="D807" t="n">
+        <v>2402.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/CME_ETHUSD_RR_latest.xlsx
+++ b/data_raw/CME_ETHUSD_RR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D807"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13346,6 +13346,70 @@
         <v>2402.33</v>
       </c>
     </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B808" t="n">
+        <v>2348.08</v>
+      </c>
+      <c r="C808" t="n">
+        <v>2336.3</v>
+      </c>
+      <c r="D808" t="n">
+        <v>2376.51</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B809" t="n">
+        <v>2340.66</v>
+      </c>
+      <c r="C809" t="n">
+        <v>2349.43</v>
+      </c>
+      <c r="D809" t="n">
+        <v>2344.43</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B810" t="n">
+        <v>2330.52</v>
+      </c>
+      <c r="C810" t="n">
+        <v>2314.34</v>
+      </c>
+      <c r="D810" t="n">
+        <v>2316.54</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B811" t="n">
+        <v>2340.24</v>
+      </c>
+      <c r="C811" t="n">
+        <v>2342.9</v>
+      </c>
+      <c r="D811" t="n">
+        <v>2305.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/CME_ETHUSD_RR_latest.xlsx
+++ b/data_raw/CME_ETHUSD_RR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D811"/>
+  <dimension ref="A1:D814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13410,6 +13410,54 @@
         <v>2305.32</v>
       </c>
     </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B812" t="n">
+        <v>2331.92</v>
+      </c>
+      <c r="C812" t="n">
+        <v>2359.04</v>
+      </c>
+      <c r="D812" t="n">
+        <v>2351.51</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B813" t="n">
+        <v>2358.78</v>
+      </c>
+      <c r="C813" t="n">
+        <v>2329.95</v>
+      </c>
+      <c r="D813" t="n">
+        <v>2306.14</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B814" t="n">
+        <v>2235.76</v>
+      </c>
+      <c r="C814" t="n">
+        <v>2228.99</v>
+      </c>
+      <c r="D814" t="n">
+        <v>2241.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
